--- a/dataset_t6_grouped/results2/G2/G2_T0860_W0027F0003T0006Z000C1N32_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T0860_W0027F0003T0006Z000C1N32_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>34.77549541499955</v>
+        <v>5.651018004937427</v>
       </c>
       <c r="D2" t="n">
-        <v>34.97653119301727</v>
+        <v>5.683686318865307</v>
       </c>
       <c r="E2" t="n">
-        <v>8.63931887533259</v>
+        <v>1.403889317241546</v>
       </c>
       <c r="F2" t="n">
-        <v>8.720758204183863</v>
+        <v>1.417123208179878</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>34.06971041643263</v>
+        <v>5.536327942670302</v>
       </c>
       <c r="D3" t="n">
-        <v>34.021186543944</v>
+        <v>5.528442813390901</v>
       </c>
       <c r="E3" t="n">
-        <v>8.63931887533259</v>
+        <v>1.403889317241546</v>
       </c>
       <c r="F3" t="n">
-        <v>8.720758204183863</v>
+        <v>1.417123208179878</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>38.25341606349468</v>
+        <v>6.216180110317885</v>
       </c>
       <c r="D4" t="n">
-        <v>38.52047307503597</v>
+        <v>6.259576874693346</v>
       </c>
       <c r="E4" t="n">
-        <v>8.63931887533259</v>
+        <v>1.403889317241546</v>
       </c>
       <c r="F4" t="n">
-        <v>8.720758204183863</v>
+        <v>1.417123208179878</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>17.44397292584795</v>
+        <v>2.834645600450292</v>
       </c>
       <c r="D5" t="n">
-        <v>17.21275164472394</v>
+        <v>2.79707214226764</v>
       </c>
       <c r="E5" t="n">
-        <v>8.63931887533259</v>
+        <v>1.403889317241546</v>
       </c>
       <c r="F5" t="n">
-        <v>8.720758204183863</v>
+        <v>1.417123208179878</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>16.9267067098293</v>
+        <v>2.750589840347261</v>
       </c>
       <c r="D6" t="n">
-        <v>17.153980207475</v>
+        <v>2.787521783714688</v>
       </c>
       <c r="E6" t="n">
-        <v>8.63931887533259</v>
+        <v>1.403889317241546</v>
       </c>
       <c r="F6" t="n">
-        <v>8.720758204183863</v>
+        <v>1.417123208179878</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>14.18173275771997</v>
+        <v>2.304531573129496</v>
       </c>
       <c r="D7" t="n">
-        <v>13.92001606434125</v>
+        <v>2.262002610455453</v>
       </c>
       <c r="E7" t="n">
-        <v>8.63931887533259</v>
+        <v>1.403889317241546</v>
       </c>
       <c r="F7" t="n">
-        <v>8.720758204183863</v>
+        <v>1.417123208179878</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>32.93492817542133</v>
+        <v>5.351925828505967</v>
       </c>
       <c r="D8" t="n">
-        <v>32.65896341085651</v>
+        <v>5.307081554264184</v>
       </c>
       <c r="E8" t="n">
-        <v>8.63931887533259</v>
+        <v>1.403889317241546</v>
       </c>
       <c r="F8" t="n">
-        <v>8.720758204183863</v>
+        <v>1.417123208179878</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>33.13145429085821</v>
+        <v>5.383861322264459</v>
       </c>
       <c r="D9" t="n">
-        <v>33.2165167760155</v>
+        <v>5.397683976102519</v>
       </c>
       <c r="E9" t="n">
-        <v>8.63931887533259</v>
+        <v>1.403889317241546</v>
       </c>
       <c r="F9" t="n">
-        <v>8.720758204183863</v>
+        <v>1.417123208179878</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>30.8670163376708</v>
+        <v>5.015890154871506</v>
       </c>
       <c r="D10" t="n">
-        <v>30.77778780076</v>
+        <v>5.001390517623499</v>
       </c>
       <c r="E10" t="n">
-        <v>8.63931887533259</v>
+        <v>1.403889317241546</v>
       </c>
       <c r="F10" t="n">
-        <v>8.720758204183863</v>
+        <v>1.417123208179878</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
